--- a/template2.xlsx
+++ b/template2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\a.baidenko\Downloads\JSQ-Laboratory\JSQ_Viewer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EC63243-03A3-4E9A-84D3-0B2E8F7DB328}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB39E88F-2431-417E-A598-C69FBFB8AA60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1665" yWindow="3120" windowWidth="27135" windowHeight="11295" xr2:uid="{AB56934D-C826-4F38-A205-E0052D29224A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AB56934D-C826-4F38-A205-E0052D29224A}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -1385,12 +1385,20 @@
       <c r="S4" s="39"/>
       <c r="T4" s="39"/>
       <c r="U4" s="40">
-        <f>IF($B$1="R290",0.00005*D4^5-0.0037*D4^4+0.1052*D4^3-1.5247*D4^2+14.856*D4-38.823,IF($B$1="R600a",0.001*D4^5-0.042*D4^4+0.6637*D4^3-5.0642*D4^2+24.812*D4-13.145,0))</f>
-        <v>-38.823</v>
+        <f>IF($B$1="R290",
+IF(OR(D4&lt;-0.48,D4&gt;41.359),"ВНЕ ДИАПАЗОНА",0.01973273385328*LN(D4+1)^4+0.2987622586022*LN(D4+1)^3+2.452863797722*LN(D4+1)^2+22.63007347287*LN(D4+1)-42.19015299063),
+IF($B$1="R600a",
+IF(OR(D4&lt;-0.79,D4&gt;32.143),"ВНЕ ДИАПАЗОНА",0.043751593072*LN(D4+1)^4+0.261943878832*LN(D4+1)^3+2.781284406656*LN(D4+1)^2+25.461831417726*LN(D4+1)-12.189730454141),
+0))</f>
+        <v>-42.190152990629997</v>
       </c>
       <c r="V4" s="41">
-        <f>IF($B$1="R290",0.00005*E4^5-0.0037*E4^4+0.1052*E4^3-1.5247*E4^2+14.856*E4-38.823,IF($B$1="R600a",0.001*E4^5-0.042*E4^4+0.6637*E4^3-5.0642*E4^2+24.812*E4-13.145,0))</f>
-        <v>-38.823</v>
+        <f>IF($B$1="R290",
+IF(OR(E4&lt;-0.48,E4&gt;41.359),"ВНЕ ДИАПАЗОНА",0.01973273385328*LN(E4+1)^4+0.2987622586022*LN(E4+1)^3+2.452863797722*LN(E4+1)^2+22.63007347287*LN(E4+1)-42.19015299063),
+IF($B$1="R600a",
+IF(OR(E4&lt;-0.79,E4&gt;32.143),"ВНЕ ДИАПАЗОНА",0.043751593072*LN(E4+1)^4+0.261943878832*LN(E4+1)^3+2.781284406656*LN(E4+1)^2+25.461831417726*LN(E4+1)-12.189730454141),
+0))</f>
+        <v>-42.190152990629997</v>
       </c>
       <c r="W4" s="42">
         <f t="shared" ref="W4" si="0">MIN(Z4:BM4)</f>
